--- a/uploads/issue_report_2026_01_02_to_2026_01_02.xlsx
+++ b/uploads/issue_report_2026_01_02_to_2026_01_02.xlsx
@@ -29,6 +29,9 @@
     <t>Quality</t>
   </si>
   <si>
+    <t>Packing</t>
+  </si>
+  <si>
     <t>Godown No</t>
   </si>
   <si>
@@ -105,9 +108,6 @@
   </si>
   <si>
     <t>Godown Total: Sel Shed</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
   </si>
 </sst>
 </file>
@@ -144,7 +144,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
       <u val="none"/>
@@ -215,13 +215,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -522,12 +524,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="0"/>
     <col min="2" max="2" width="20" customWidth="true" style="0"/>
-    <col min="3" max="3" width="15" customWidth="true" style="0"/>
     <col min="4" max="4" width="16" customWidth="true" style="0"/>
     <col min="5" max="5" width="16" customWidth="true" style="0"/>
     <col min="6" max="6" width="16" customWidth="true" style="0"/>
@@ -540,17 +541,17 @@
     <col min="13" max="13" width="16" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -590,647 +591,598 @@
       <c r="M4" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="4">
         <v>150</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4">
+      <c r="C5" s="4">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="4">
         <v>31</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>4389.0</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
       <c r="G5" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="4">
         <v>21</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>2973.0</v>
       </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
       <c r="K5" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M5" s="4">
         <v>10</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5">
         <v>1416.0</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="4">
         <v>793</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="E6" s="4">
         <v>7</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>1020.0</v>
       </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
       <c r="G6" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I6" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K6" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M6" s="4">
         <v>7</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6">
         <v>1020.0</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="4">
         <v>760</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4">
         <v>10</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>1467.0</v>
       </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
       <c r="G7" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K7" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="4">
         <v>10</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7">
         <v>1467.0</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="4">
         <v>754</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E8" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="G8" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="4">
         <v>10</v>
       </c>
-      <c r="I8" s="4">
-        <v>0.0</v>
-      </c>
       <c r="J8" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K8" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="4">
         <v>-10</v>
       </c>
-      <c r="M8" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="N8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
         <v>48</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="6">
         <v>6876.0</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="6">
         <v>31</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="6">
         <v>2973.0</v>
       </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="6">
         <v>17</v>
       </c>
-      <c r="M9" s="5">
+      <c r="N9" s="6">
         <v>3903.0</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="4">
         <v>797</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4">
         <v>5</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
         <v>2200.0</v>
       </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
       <c r="G10" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K10" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L10" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M10" s="4">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>2200.0</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="4">
         <v>796</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="4">
         <v>5</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
         <v>3280.0</v>
       </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
       <c r="G11" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K11" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11">
         <v>3280.0</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
         <v>5480.0</v>
       </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
         <v>5480.0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" s="4">
         <v>466</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="4">
+      <c r="C13" s="4">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4">
         <v>6151</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>375160.0</v>
       </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
       <c r="G13" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="4">
         <v>6151</v>
       </c>
-      <c r="M13" s="4">
+      <c r="N13">
         <v>375160.0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5">
+    <row r="14" spans="1:14">
+      <c r="A14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
         <v>6151</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="6">
         <v>375160.0</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="5">
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="6">
         <v>6151</v>
       </c>
-      <c r="M14" s="5">
+      <c r="N14" s="6">
         <v>375160.0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="4">
         <v>150</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="4">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="4">
         <v>100</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>4165.0</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I15" s="4">
-        <v>0.0</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4">
-        <v>0</v>
+        <v>2500.0</v>
       </c>
       <c r="K15" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4">
-        <v>100</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="4">
-        <v>4165.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>40</v>
+      </c>
+      <c r="N15">
+        <v>1665.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="C16" s="4">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="E16" s="4">
-        <v>0.0</v>
+        <v>65</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>2710.0</v>
       </c>
       <c r="G16" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>60</v>
+        <v>0.0</v>
       </c>
       <c r="I16" s="4">
-        <v>0.0</v>
+        <v>65</v>
       </c>
       <c r="J16" s="4">
-        <v>0</v>
+        <v>2709.0</v>
       </c>
       <c r="K16" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L16" s="4">
-        <v>-60</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="4">
-        <v>160</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="4">
-        <v>65</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2710.0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="4">
-        <v>65</v>
-      </c>
-      <c r="M17" s="4">
-        <v>2710.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="4">
-        <v>160</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="4">
-        <v>65</v>
-      </c>
-      <c r="I18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-65</v>
-      </c>
-      <c r="M18" s="4">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
         <v>165</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F17" s="6">
         <v>6875.0</v>
       </c>
-      <c r="F19" s="5">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="5">
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="6">
         <v>125</v>
       </c>
-      <c r="I19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="5">
+      <c r="J17" s="6">
+        <v>5209.0</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M17" s="6">
         <v>40</v>
       </c>
-      <c r="M19" s="5">
-        <v>6875.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6">
+      <c r="N17" s="5">
+        <v>1666.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8">
         <v>6364</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F19" s="8">
         <v>394391.0</v>
       </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="6">
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="8">
         <v>156</v>
       </c>
-      <c r="I21" s="6">
-        <v>2973.0</v>
-      </c>
-      <c r="J21" s="6">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="J19" s="8">
+        <v>8182.0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="8">
         <v>6208</v>
       </c>
-      <c r="M21" s="6">
-        <v>391418.0</v>
+      <c r="N19" s="7">
+        <v>386209.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/uploads/issue_report_2026_01_02_to_2026_01_02.xlsx
+++ b/uploads/issue_report_2026_01_02_to_2026_01_02.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>THE EMPIRE JUTE COMPANY LTD.</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>HABIZABI</t>
-  </si>
-  <si>
-    <t>M-J-6(B.BOT)</t>
   </si>
   <si>
     <t>M6 (B.BOT)</t>
@@ -524,7 +521,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="0"/>
@@ -685,7 +682,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="4">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -709,10 +706,10 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4">
-        <v>0.0</v>
+        <v>1467.0</v>
       </c>
       <c r="K7" s="4">
         <v>0</v>
@@ -721,97 +718,97 @@
         <v>0.0</v>
       </c>
       <c r="M7" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1467.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="4">
-        <v>754</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="4">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
+        <v>48</v>
+      </c>
+      <c r="F8" s="6">
+        <v>6876.0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>31</v>
+      </c>
+      <c r="J8" s="6">
+        <v>4440.0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="6">
         <v>17</v>
       </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>10</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>-10</v>
-      </c>
-      <c r="N8">
-        <v>0.0</v>
+      <c r="N8" s="6">
+        <v>2436.0</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4">
+        <v>797</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6">
-        <v>48</v>
-      </c>
-      <c r="F9" s="6">
-        <v>6876.0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>31</v>
-      </c>
-      <c r="J9" s="6">
-        <v>2973.0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>17</v>
-      </c>
-      <c r="N9" s="6">
-        <v>3903.0</v>
+      <c r="C9" s="4">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2200.0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>2200.0</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>22</v>
@@ -826,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <v>2200.0</v>
+        <v>3280.0</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -850,191 +847,191 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>2200.0</v>
+        <v>3280.0</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="4">
-        <v>796</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="4">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>5480.0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <v>5480.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4">
+        <v>466</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4">
+        <v>6151</v>
+      </c>
+      <c r="F12" s="4">
+        <v>375160.0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>6151</v>
+      </c>
+      <c r="N12">
+        <v>375160.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <v>6151</v>
+      </c>
+      <c r="F13" s="6">
+        <v>375160.0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>6151</v>
+      </c>
+      <c r="N13" s="6">
+        <v>375160.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4">
+        <v>150</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4">
         <v>5</v>
       </c>
-      <c r="D11" s="4">
-        <v>5</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>3280.0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>3280.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>5480.0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="6">
-        <v>5480.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4">
-        <v>466</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4">
-        <v>6151</v>
-      </c>
-      <c r="F13" s="4">
-        <v>375160.0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="4">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="M13" s="4">
-        <v>6151</v>
-      </c>
-      <c r="N13">
-        <v>375160.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6">
-        <v>6151</v>
-      </c>
-      <c r="F14" s="6">
-        <v>375160.0</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="M14" s="6">
-        <v>6151</v>
-      </c>
-      <c r="N14" s="6">
-        <v>375160.0</v>
+      <c r="E14" s="4">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4">
+        <v>4165.0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>60</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2500.0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <v>1665.0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4">
         <v>5</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="4">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F15" s="4">
-        <v>4165.0</v>
+        <v>2710.0</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
@@ -1043,10 +1040,10 @@
         <v>0.0</v>
       </c>
       <c r="I15" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J15" s="4">
-        <v>2500.0</v>
+        <v>2709.0</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>
@@ -1055,128 +1052,84 @@
         <v>0.0</v>
       </c>
       <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6">
+        <v>165</v>
+      </c>
+      <c r="F16" s="6">
+        <v>6875.0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>125</v>
+      </c>
+      <c r="J16" s="6">
+        <v>5209.0</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="6">
         <v>40</v>
       </c>
-      <c r="N15">
-        <v>1665.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="4">
-        <v>160</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="4">
-        <v>5</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="4">
-        <v>65</v>
-      </c>
-      <c r="F16" s="4">
-        <v>2710.0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>65</v>
-      </c>
-      <c r="J16" s="4">
-        <v>2709.0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
-        <v>165</v>
-      </c>
-      <c r="F17" s="6">
-        <v>6875.0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="6">
-        <v>125</v>
-      </c>
-      <c r="J17" s="6">
-        <v>5209.0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="6">
-        <v>40</v>
-      </c>
-      <c r="N17" s="5">
+      <c r="N16" s="5">
         <v>1666.0</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8">
+    <row r="18" spans="1:14">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8">
         <v>6364</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F18" s="8">
         <v>394391.0</v>
       </c>
-      <c r="G19" s="8">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="8">
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="8">
         <v>156</v>
       </c>
-      <c r="J19" s="8">
-        <v>8182.0</v>
-      </c>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="8">
+      <c r="J18" s="8">
+        <v>9649.0</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="8">
         <v>6208</v>
       </c>
-      <c r="N19" s="7">
-        <v>386209.0</v>
+      <c r="N18" s="7">
+        <v>384742.0</v>
       </c>
     </row>
   </sheetData>
